--- a/data/exports/crudo_2026-01-01_2030-12-31.xlsx
+++ b/data/exports/crudo_2026-01-01_2030-12-31.xlsx
@@ -1301,7 +1301,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>10.10.2026 01:12</t>
+          <t>10.10.2026 01:21</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1339,7 +1339,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>10.10.2026 01:12</t>
+          <t>10.10.2026 01:21</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">

--- a/data/exports/crudo_2026-01-01_2030-12-31.xlsx
+++ b/data/exports/crudo_2026-01-01_2030-12-31.xlsx
@@ -1301,7 +1301,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>10.10.2026 01:21</t>
+          <t>10.10.2026 01:30</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1339,7 +1339,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>10.10.2026 01:21</t>
+          <t>10.10.2026 01:30</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">

--- a/data/exports/crudo_2026-01-01_2030-12-31.xlsx
+++ b/data/exports/crudo_2026-01-01_2030-12-31.xlsx
@@ -1301,7 +1301,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>10.10.2026 01:30</t>
+          <t>10.10.2026 01:40</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1339,7 +1339,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>10.10.2026 01:30</t>
+          <t>10.10.2026 01:40</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">

--- a/data/exports/crudo_2026-01-01_2030-12-31.xlsx
+++ b/data/exports/crudo_2026-01-01_2030-12-31.xlsx
@@ -1301,7 +1301,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>10.10.2026 01:40</t>
+          <t>10.10.2026 01:42</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1339,7 +1339,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>10.10.2026 01:40</t>
+          <t>10.10.2026 01:42</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">

--- a/data/exports/crudo_2026-01-01_2030-12-31.xlsx
+++ b/data/exports/crudo_2026-01-01_2030-12-31.xlsx
@@ -1301,7 +1301,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>10.10.2026 01:42</t>
+          <t>10.10.2026 03:45</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1339,7 +1339,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>10.10.2026 01:42</t>
+          <t>10.10.2026 03:45</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">

--- a/data/exports/crudo_2026-01-01_2030-12-31.xlsx
+++ b/data/exports/crudo_2026-01-01_2030-12-31.xlsx
@@ -1301,7 +1301,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>10.10.2026 03:45</t>
+          <t>10.10.2026 03:47</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1339,7 +1339,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>10.10.2026 03:45</t>
+          <t>10.10.2026 03:47</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">

--- a/data/exports/crudo_2026-01-01_2030-12-31.xlsx
+++ b/data/exports/crudo_2026-01-01_2030-12-31.xlsx
@@ -1301,7 +1301,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>10.10.2026 03:47</t>
+          <t>10.10.2026 03:50</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1339,7 +1339,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>10.10.2026 03:47</t>
+          <t>10.10.2026 03:50</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">

--- a/data/exports/crudo_2026-01-01_2030-12-31.xlsx
+++ b/data/exports/crudo_2026-01-01_2030-12-31.xlsx
@@ -1301,7 +1301,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>10.10.2026 03:50</t>
+          <t>10.10.2026 03:56</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1339,7 +1339,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>10.10.2026 03:50</t>
+          <t>10.10.2026 03:56</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">

--- a/data/exports/crudo_2026-01-01_2030-12-31.xlsx
+++ b/data/exports/crudo_2026-01-01_2030-12-31.xlsx
@@ -1301,7 +1301,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>10.10.2026 03:56</t>
+          <t>10.10.2026 04:03</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1339,7 +1339,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>10.10.2026 03:56</t>
+          <t>10.10.2026 04:03</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">

--- a/data/exports/crudo_2026-01-01_2030-12-31.xlsx
+++ b/data/exports/crudo_2026-01-01_2030-12-31.xlsx
@@ -1301,7 +1301,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>10.10.2026 04:03</t>
+          <t>10.10.2026 23:33</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1339,7 +1339,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>10.10.2026 04:03</t>
+          <t>10.10.2026 23:33</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">

--- a/data/exports/crudo_2026-01-01_2030-12-31.xlsx
+++ b/data/exports/crudo_2026-01-01_2030-12-31.xlsx
@@ -930,7 +930,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -1301,7 +1301,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>10.10.2026 23:33</t>
+          <t>15.10.2026 16:06</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1339,7 +1339,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>10.10.2026 23:33</t>
+          <t>15.10.2026 16:06</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">

--- a/data/exports/crudo_2026-01-01_2030-12-31.xlsx
+++ b/data/exports/crudo_2026-01-01_2030-12-31.xlsx
@@ -1301,7 +1301,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>15.10.2026 16:06</t>
+          <t>15.10.2026 16:11</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1339,7 +1339,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>15.10.2026 16:06</t>
+          <t>15.10.2026 16:11</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">

--- a/data/exports/crudo_2026-01-01_2030-12-31.xlsx
+++ b/data/exports/crudo_2026-01-01_2030-12-31.xlsx
@@ -1301,7 +1301,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>15.10.2026 16:11</t>
+          <t>15.10.2026 16:20</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1339,7 +1339,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>15.10.2026 16:11</t>
+          <t>15.10.2026 16:20</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">

--- a/data/exports/crudo_2026-01-01_2030-12-31.xlsx
+++ b/data/exports/crudo_2026-01-01_2030-12-31.xlsx
@@ -1301,7 +1301,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>15.10.2026 16:20</t>
+          <t>15.10.2026 16:33</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1339,7 +1339,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>15.10.2026 16:20</t>
+          <t>15.10.2026 16:33</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">

--- a/data/exports/crudo_2026-01-01_2030-12-31.xlsx
+++ b/data/exports/crudo_2026-01-01_2030-12-31.xlsx
@@ -930,7 +930,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -1301,7 +1301,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>15.10.2026 16:33</t>
+          <t>16.10.2026 18:39</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1339,7 +1339,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>15.10.2026 16:33</t>
+          <t>16.10.2026 18:39</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">

--- a/data/exports/crudo_2026-01-01_2030-12-31.xlsx
+++ b/data/exports/crudo_2026-01-01_2030-12-31.xlsx
@@ -1301,7 +1301,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>16.10.2026 18:39</t>
+          <t>16.10.2026 21:08</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1339,7 +1339,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>16.10.2026 18:39</t>
+          <t>16.10.2026 21:08</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">

--- a/data/exports/crudo_2026-01-01_2030-12-31.xlsx
+++ b/data/exports/crudo_2026-01-01_2030-12-31.xlsx
@@ -1301,7 +1301,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>16.10.2026 21:08</t>
+          <t>16.10.2026 21:21</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1339,7 +1339,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>16.10.2026 21:08</t>
+          <t>16.10.2026 21:21</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">

--- a/data/exports/crudo_2026-01-01_2030-12-31.xlsx
+++ b/data/exports/crudo_2026-01-01_2030-12-31.xlsx
@@ -1301,7 +1301,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>16.10.2026 21:21</t>
+          <t>16.10.2026 21:24</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1339,7 +1339,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>16.10.2026 21:21</t>
+          <t>16.10.2026 21:24</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
